--- a/banco_de_dados/entrega_orientadora/Dicionario_Variaveis_Projeto.xlsx
+++ b/banco_de_dados/entrega_orientadora/Dicionario_Variaveis_Projeto.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="268">
   <si>
     <t>variavel</t>
   </si>
@@ -148,6 +148,15 @@
     <t>V00118</t>
   </si>
   <si>
+    <t>V00199</t>
+  </si>
+  <si>
+    <t>V00200</t>
+  </si>
+  <si>
+    <t>V00201</t>
+  </si>
+  <si>
     <t>V00236</t>
   </si>
   <si>
@@ -205,9 +214,15 @@
     <t>V01321</t>
   </si>
   <si>
+    <t>V06001</t>
+  </si>
+  <si>
     <t>V06004</t>
   </si>
   <si>
+    <t>V06005</t>
+  </si>
+  <si>
     <t>V01031</t>
   </si>
   <si>
@@ -349,6 +364,15 @@
     <t>Domicílios Particulares Permanentes Ocupados, Utiliza outra forma de abastecimento de água</t>
   </si>
   <si>
+    <t>Domicílios Particulares Permanentes Ocupados, Água chega encanada até dentro da casa, apartamento ou habitação</t>
+  </si>
+  <si>
+    <t>Domicílios Particulares Permanentes Ocupados, Água chega encanada, mas apenas ao terreno</t>
+  </si>
+  <si>
+    <t>Domicílios Particulares Permanentes Ocupados, Água não chega encanada ao domicílio</t>
+  </si>
+  <si>
     <t>Domicílios Particulares Permanentes Ocupados, Apenas banheiro de uso comum a mais de um domicílio</t>
   </si>
   <si>
@@ -403,9 +427,15 @@
     <t>Cor ou raça é indígena</t>
   </si>
   <si>
+    <t>Pessoas responsáveis em domicílios particulares permanentes ocupados</t>
+  </si>
+  <si>
     <t>Valor do rendimento nominal médio mensal das pessoas responsáveis com rendimentos por domicílios particulares permanentes ocupados</t>
   </si>
   <si>
+    <t>Variância do rendimento nominal mensal das pessoas responsáveis com rendimentos por domicílios particulares permanentes ocupados</t>
+  </si>
+  <si>
     <t>0 a 4 anos</t>
   </si>
   <si>
@@ -508,7 +538,7 @@
     <t>pct_raca_pretpardind, pct_crianca_0a4, pct_pop_0a14, pct_idoso_60mais</t>
   </si>
   <si>
-    <t>pct_agua_inad, pct_esgoto_inad, pct_lixo_inad, razao_moradores, pct_dom_improv, pct_hab_precaria, pct_moradia_convencional, pct_moradia_nao_convencional, pct_apartamento, pct_casa, pct_casa_vila_condominio, pct_sem_banheiro, pct_sem_banheiro_nem_sanitario</t>
+    <t>pct_agua_inad, pct_esgoto_inad, pct_lixo_inad, razao_moradores, pct_dom_improv, pct_hab_precaria, pct_moradia_convencional, pct_moradia_nao_convencional, pct_apartamento, pct_casa, pct_casa_vila_condominio, pct_sem_agua_canalizada, pct_agua_nao_encanada, pct_agua_so_terreno, pct_sem_banheiro, pct_sem_banheiro_nem_sanitario</t>
   </si>
   <si>
     <t>razao_moradores, pct_dom_improv, pct_hab_precaria</t>
@@ -538,6 +568,18 @@
     <t>pct_agua_inad</t>
   </si>
   <si>
+    <t>pct_sem_agua_canalizada</t>
+  </si>
+  <si>
+    <t>pct_agua_so_terreno</t>
+  </si>
+  <si>
+    <t>pct_agua_nao_encanada</t>
+  </si>
+  <si>
+    <t>(conferência) banheiro de uso comum; completa o bloco de banheiro junto de V00238 e V00495</t>
+  </si>
+  <si>
     <t>pct_sem_banheiro_nem_sanitario</t>
   </si>
   <si>
@@ -556,9 +598,15 @@
     <t>pct_raca_pretpardind</t>
   </si>
   <si>
+    <t>(auditoria da renda) quantas pessoas responsáveis sustentam a média do V06004</t>
+  </si>
+  <si>
     <t>renda_media</t>
   </si>
   <si>
+    <t>(auditoria da renda) variância do rendimento; CV = √V06005/V06004 separa setor rico de setor com poucas declarações enormes</t>
+  </si>
+  <si>
     <t>pct_crianca_0a4, pct_pop_0a14, iep_setor</t>
   </si>
   <si>
@@ -571,6 +619,9 @@
     <t>pct_idoso_60mais, iep_setor, rdi_setor, prop_70mais_entre_60mais</t>
   </si>
   <si>
+    <t>(conferência) total de pessoas responsáveis; confere V01062+V01063 e documenta o denominador ABANDONADO em 22/05/2026 — é contagem de pessoas, não de domicílios</t>
+  </si>
+  <si>
     <t>pct_resp_feminino</t>
   </si>
   <si>
@@ -740,6 +791,15 @@
   </si>
   <si>
     <t>Proporção de domicílios do tipo casa de vila ou em condomínio</t>
+  </si>
+  <si>
+    <t>Proporção de domicílios em que a água não chega encanada até dentro do domicílio (complemento de V00199; equivale a V00200+V00201 sobre V00001)</t>
+  </si>
+  <si>
+    <t>Proporção de domicílios em que a água não chega encanada ao domicílio (V00201)</t>
+  </si>
+  <si>
+    <t>Proporção de domicílios em que a água chega encanada apenas ao terreno (V00200)</t>
   </si>
   <si>
     <t>Proporção de domicílios sem banheiro de uso exclusivo com chuveiro e vaso sanitário</t>
@@ -773,16 +833,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -798,7 +850,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -806,30 +858,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1124,7 +1158,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1133,28 +1167,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1163,25 +1197,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E2" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H2" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1189,25 +1223,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E3" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H3" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1215,25 +1249,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E4" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H4" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1241,25 +1275,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E5" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H5" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1267,25 +1301,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E6" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H6" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1293,25 +1327,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E7" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H7" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1319,25 +1353,25 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E8" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H8" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1345,25 +1379,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E9" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H9" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1371,25 +1405,25 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D10" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E10" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="H10" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1397,25 +1431,25 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E11" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H11" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1423,25 +1457,25 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E12" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H12" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1449,25 +1483,25 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E13" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F13" t="s">
         <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="H13" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1475,25 +1509,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E14" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F14" t="s">
         <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="H14" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1501,25 +1535,25 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D15" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E15" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F15" t="s">
         <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="H15" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1527,25 +1561,25 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D16" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E16" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H16" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1553,25 +1587,25 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D17" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E17" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F17" t="s">
         <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H17" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1579,25 +1613,25 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D18" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E18" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F18" t="s">
         <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="H18" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1605,25 +1639,25 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E19" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F19" t="s">
         <v>17</v>
       </c>
       <c r="G19" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="H19" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1631,25 +1665,25 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E20" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F20" t="s">
         <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="H20" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1657,25 +1691,25 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E21" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F21" t="s">
         <v>17</v>
       </c>
       <c r="G21" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="H21" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1683,25 +1717,25 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D22" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E22" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F22" t="s">
         <v>17</v>
       </c>
       <c r="G22" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H22" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1709,25 +1743,25 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C23" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D23" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E23" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F23" t="s">
         <v>17</v>
       </c>
       <c r="G23" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H23" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1735,25 +1769,25 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D24" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E24" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F24" t="s">
         <v>17</v>
       </c>
       <c r="G24" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H24" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1761,25 +1795,25 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D25" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E25" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F25" t="s">
         <v>17</v>
       </c>
       <c r="G25" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H25" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1787,25 +1821,25 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D26" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E26" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F26" t="s">
         <v>17</v>
       </c>
       <c r="G26" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H26" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1813,25 +1847,25 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D27" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E27" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F27" t="s">
         <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H27" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1839,25 +1873,25 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D28" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E28" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F28" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G28" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H28" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1865,25 +1899,25 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C29" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D29" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E29" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F29" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G29" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H29" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1891,25 +1925,25 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C30" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D30" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E30" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F30" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G30" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H30" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1917,25 +1951,25 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D31" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E31" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F31" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G31" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H31" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1943,25 +1977,25 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C32" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D32" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E32" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F32" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G32" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H32" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1969,25 +2003,25 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D33" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E33" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F33" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G33" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H33" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1995,25 +2029,25 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C34" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D34" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E34" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F34" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G34" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H34" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2021,25 +2055,25 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C35" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D35" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E35" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F35" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G35" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="H35" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -2047,25 +2081,25 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C36" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D36" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E36" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F36" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G36" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="H36" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2073,25 +2107,25 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C37" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D37" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E37" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F37" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G37" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="H37" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -2099,25 +2133,25 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C38" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D38" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E38" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F38" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G38" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="H38" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2125,25 +2159,25 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C39" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D39" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E39" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F39" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G39" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="H39" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -2151,25 +2185,25 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C40" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D40" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E40" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F40" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G40" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="H40" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2177,25 +2211,25 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C41" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D41" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E41" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F41" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G41" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="H41" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -2203,25 +2237,25 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C42" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D42" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E42" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F42" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G42" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="H42" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2229,25 +2263,25 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C43" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D43" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E43" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F43" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G43" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="H43" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2255,25 +2289,25 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C44" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D44" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E44" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F44" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G44" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="H44" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -2281,25 +2315,25 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C45" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D45" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E45" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F45" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G45" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="H45" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2307,25 +2341,25 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C46" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D46" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E46" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F46" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G46" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="H46" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -2333,25 +2367,25 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C47" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D47" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E47" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F47" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G47" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="H47" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -2359,25 +2393,25 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="C48" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D48" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E48" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F48" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G48" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="H48" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2385,25 +2419,25 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C49" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D49" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="E49" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F49" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="G49" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="H49" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -2411,25 +2445,25 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C50" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D50" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="E50" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F50" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="G50" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="H50" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -2437,25 +2471,25 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="C51" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D51" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="E51" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F51" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="G51" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="H51" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -2463,25 +2497,25 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="D52" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="E52" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F52" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G52" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="H52" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2489,25 +2523,25 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C53" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="D53" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="E53" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F53" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G53" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="H53" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2515,25 +2549,25 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C54" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D54" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="E54" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="F54" t="s">
         <v>9</v>
       </c>
       <c r="G54" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="H54" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2541,25 +2575,25 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C55" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D55" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E55" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="F55" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="H55" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2567,25 +2601,25 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C56" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D56" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E56" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="F56" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G56" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="H56" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2593,25 +2627,25 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C57" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D57" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E57" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="F57" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G57" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="H57" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2619,25 +2653,25 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C58" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D58" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E58" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G58" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H58" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2645,25 +2679,25 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C59" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D59" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E59" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="F59" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G59" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="H59" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2671,25 +2705,25 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C60" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D60" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E60" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F60" t="s">
         <v>17</v>
       </c>
       <c r="G60" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="H60" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2697,25 +2731,25 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C61" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D61" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E61" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F61" t="s">
         <v>17</v>
       </c>
       <c r="G61" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="H61" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2723,25 +2757,25 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C62" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D62" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E62" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F62" t="s">
         <v>17</v>
       </c>
       <c r="G62" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="H62" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2749,25 +2783,25 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C63" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D63" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E63" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F63" t="s">
         <v>17</v>
       </c>
       <c r="G63" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="H63" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2775,25 +2809,25 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C64" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D64" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E64" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F64" t="s">
         <v>17</v>
       </c>
       <c r="G64" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="H64" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2801,25 +2835,25 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C65" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D65" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E65" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F65" t="s">
         <v>17</v>
       </c>
       <c r="G65" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="H65" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2827,25 +2861,25 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C66" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D66" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="E66" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="F66" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G66" t="s">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="H66" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2853,25 +2887,25 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C67" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D67" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="E67" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="F67" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G67" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="H67" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2879,25 +2913,155 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C68" t="s">
+        <v>157</v>
+      </c>
+      <c r="D68" t="s">
+        <v>157</v>
+      </c>
+      <c r="E68" t="s">
+        <v>167</v>
+      </c>
+      <c r="F68" t="s">
+        <v>17</v>
+      </c>
+      <c r="G68" t="s">
+        <v>196</v>
+      </c>
+      <c r="H68" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" t="s">
+        <v>157</v>
+      </c>
+      <c r="D69" t="s">
+        <v>157</v>
+      </c>
+      <c r="E69" t="s">
+        <v>167</v>
+      </c>
+      <c r="F69" t="s">
+        <v>17</v>
+      </c>
+      <c r="G69" t="s">
+        <v>197</v>
+      </c>
+      <c r="H69" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" t="s">
+        <v>147</v>
+      </c>
+      <c r="C70" t="s">
+        <v>157</v>
+      </c>
+      <c r="D70" t="s">
+        <v>157</v>
+      </c>
+      <c r="E70" t="s">
+        <v>167</v>
+      </c>
+      <c r="F70" t="s">
+        <v>17</v>
+      </c>
+      <c r="G70" t="s">
+        <v>197</v>
+      </c>
+      <c r="H70" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" t="s">
         <v>148</v>
       </c>
-      <c r="D68" t="s">
-        <v>148</v>
-      </c>
-      <c r="E68" t="s">
+      <c r="C71" t="s">
         <v>158</v>
       </c>
-      <c r="F68" t="s">
+      <c r="D71" t="s">
+        <v>158</v>
+      </c>
+      <c r="E71" t="s">
+        <v>168</v>
+      </c>
+      <c r="F71" t="s">
         <v>9</v>
       </c>
-      <c r="G68" t="s">
-        <v>182</v>
-      </c>
-      <c r="H68" t="s">
-        <v>184</v>
+      <c r="G71" t="s">
+        <v>198</v>
+      </c>
+      <c r="H71" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" t="s">
+        <v>149</v>
+      </c>
+      <c r="C72" t="s">
+        <v>158</v>
+      </c>
+      <c r="D72" t="s">
+        <v>158</v>
+      </c>
+      <c r="E72" t="s">
+        <v>168</v>
+      </c>
+      <c r="F72" t="s">
+        <v>9</v>
+      </c>
+      <c r="G72" t="s">
+        <v>199</v>
+      </c>
+      <c r="H72" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" t="s">
+        <v>150</v>
+      </c>
+      <c r="C73" t="s">
+        <v>158</v>
+      </c>
+      <c r="D73" t="s">
+        <v>158</v>
+      </c>
+      <c r="E73" t="s">
+        <v>168</v>
+      </c>
+      <c r="F73" t="s">
+        <v>9</v>
+      </c>
+      <c r="G73" t="s">
+        <v>199</v>
+      </c>
+      <c r="H73" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -2916,107 +3080,107 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C2" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="D2" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="H2" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="H3" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E4" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="H4" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -3026,7 +3190,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -3035,290 +3199,290 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>191</v>
+      <c r="A1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1" t="s">
+        <v>207</v>
+      </c>
+      <c r="G1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="B2" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C2" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="D2" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G2" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="B3" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C3" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="D3" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G3" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="B4" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C4" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="D4" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G4" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="B5" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="C5" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="D5" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="E5" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="F5" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="G5" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="B6" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="C6" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="F6" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G6" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="B7" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="C7" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="F7" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="G7" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="B8" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="C8" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="D8" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G8" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="B9" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C9" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D9" t="s">
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="F9" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G9" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="B10" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C10" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D10" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="E10" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="F10" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G10" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="B11" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C11" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D11" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G11" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="B12" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C12" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D12" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="E12" t="s">
         <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G12" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="B13" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C13" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
@@ -3327,21 +3491,21 @@
         <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G13" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="B14" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C14" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D14" t="s">
         <v>22</v>
@@ -3350,21 +3514,21 @@
         <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G14" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="B15" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C15" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D15" t="s">
         <v>23</v>
@@ -3373,56 +3537,56 @@
         <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G15" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C16" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E16" t="s">
         <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G16" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C17" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E17" t="s">
         <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G17" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3430,68 +3594,68 @@
         <v>182</v>
       </c>
       <c r="B18" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="C18" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G18" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B19" t="s">
-        <v>147</v>
+        <v>219</v>
       </c>
       <c r="C19" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F19" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G19" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="B20" t="s">
-        <v>147</v>
+        <v>219</v>
       </c>
       <c r="C20" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D20" t="s">
-        <v>215</v>
+        <v>45</v>
       </c>
       <c r="E20" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G20" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3499,91 +3663,160 @@
         <v>199</v>
       </c>
       <c r="B21" t="s">
-        <v>147</v>
+        <v>220</v>
       </c>
       <c r="C21" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D21" t="s">
-        <v>216</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
-        <v>16</v>
+        <v>237</v>
       </c>
       <c r="F21" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G21" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C22" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D22" t="s">
-        <v>216</v>
+        <v>66</v>
       </c>
       <c r="E22" t="s">
-        <v>215</v>
+        <v>16</v>
       </c>
       <c r="F22" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="G22" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C23" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D23" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="E23" t="s">
-        <v>221</v>
+        <v>16</v>
       </c>
       <c r="F23" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="G23" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="B24" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C24" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D24" t="s">
-        <v>71</v>
+        <v>233</v>
       </c>
       <c r="E24" t="s">
-        <v>216</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="G24" t="s">
-        <v>247</v>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>217</v>
+      </c>
+      <c r="B25" t="s">
+        <v>157</v>
+      </c>
+      <c r="C25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D25" t="s">
+        <v>233</v>
+      </c>
+      <c r="E25" t="s">
+        <v>232</v>
+      </c>
+      <c r="F25" t="s">
+        <v>241</v>
+      </c>
+      <c r="G25" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>196</v>
+      </c>
+      <c r="B26" t="s">
+        <v>157</v>
+      </c>
+      <c r="C26" t="s">
+        <v>223</v>
+      </c>
+      <c r="D26" t="s">
+        <v>233</v>
+      </c>
+      <c r="E26" t="s">
+        <v>238</v>
+      </c>
+      <c r="F26" t="s">
+        <v>241</v>
+      </c>
+      <c r="G26" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>218</v>
+      </c>
+      <c r="B27" t="s">
+        <v>157</v>
+      </c>
+      <c r="C27" t="s">
+        <v>223</v>
+      </c>
+      <c r="D27" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" t="s">
+        <v>233</v>
+      </c>
+      <c r="F27" t="s">
+        <v>241</v>
+      </c>
+      <c r="G27" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -3602,28 +3835,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3632,25 +3865,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E2" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H2" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3658,25 +3891,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E3" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H3" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -3684,25 +3917,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E4" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H4" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3710,25 +3943,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E5" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H5" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3736,25 +3969,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E6" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H6" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3762,25 +3995,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E7" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H7" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -3788,25 +4021,25 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E8" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H8" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3814,25 +4047,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E9" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H9" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3840,25 +4073,25 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D10" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E10" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="H10" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -3877,28 +4110,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3907,25 +4140,25 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E2" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H2" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3933,25 +4166,25 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E3" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H3" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -3959,25 +4192,25 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="H4" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3985,25 +4218,25 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E5" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="H5" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4011,25 +4244,25 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E6" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="H6" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4037,25 +4270,25 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E7" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H7" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4063,25 +4296,25 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E8" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H8" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4089,25 +4322,25 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D9" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E9" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="H9" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4115,25 +4348,25 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E10" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="H10" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -4141,25 +4374,25 @@
         <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E11" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="H11" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -4167,25 +4400,25 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E12" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="H12" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -4193,25 +4426,25 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E13" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F13" t="s">
         <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H13" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -4219,25 +4452,25 @@
         <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E14" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F14" t="s">
         <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H14" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4245,25 +4478,25 @@
         <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D15" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E15" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F15" t="s">
         <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H15" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -4271,25 +4504,25 @@
         <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D16" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E16" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H16" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -4297,25 +4530,25 @@
         <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C17" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D17" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E17" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F17" t="s">
         <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H17" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -4323,25 +4556,25 @@
         <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D18" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E18" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F18" t="s">
         <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H18" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -4351,7 +4584,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -4360,28 +4593,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4390,25 +4623,25 @@
         <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D2" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G2" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H2" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4416,25 +4649,25 @@
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D3" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G3" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H3" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4442,25 +4675,25 @@
         <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G4" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H4" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4468,25 +4701,25 @@
         <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G5" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H5" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4494,25 +4727,25 @@
         <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C6" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D6" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G6" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H6" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4520,25 +4753,25 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C7" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E7" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G7" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H7" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4546,25 +4779,25 @@
         <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C8" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E8" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G8" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H8" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4572,25 +4805,25 @@
         <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D9" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E9" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G9" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="H9" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4598,25 +4831,25 @@
         <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D10" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E10" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="H10" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -4624,25 +4857,25 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C11" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E11" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G11" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="H11" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -4650,25 +4883,25 @@
         <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E12" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G12" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="H12" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -4676,25 +4909,25 @@
         <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C13" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E13" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G13" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="H13" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -4702,25 +4935,25 @@
         <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C14" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D14" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E14" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G14" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="H14" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4728,25 +4961,25 @@
         <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C15" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D15" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E15" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G15" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="H15" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -4754,25 +4987,25 @@
         <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D16" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E16" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G16" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="H16" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -4780,25 +5013,25 @@
         <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C17" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D17" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E17" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F17" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G17" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="H17" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -4806,25 +5039,25 @@
         <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C18" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D18" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E18" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="H18" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -4832,25 +5065,25 @@
         <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C19" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D19" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E19" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F19" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="H19" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -4858,25 +5091,25 @@
         <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C20" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D20" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E20" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="H20" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -4884,25 +5117,25 @@
         <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C21" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D21" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E21" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F21" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="H21" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -4910,25 +5143,103 @@
         <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="C22" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D22" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E22" t="s">
+        <v>163</v>
+      </c>
+      <c r="F22" t="s">
+        <v>57</v>
+      </c>
+      <c r="G22" t="s">
+        <v>187</v>
+      </c>
+      <c r="H22" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" t="s">
         <v>153</v>
       </c>
-      <c r="F22" t="s">
-        <v>54</v>
-      </c>
-      <c r="G22" t="s">
-        <v>159</v>
-      </c>
-      <c r="H22" t="s">
-        <v>183</v>
+      <c r="D23" t="s">
+        <v>160</v>
+      </c>
+      <c r="E23" t="s">
+        <v>163</v>
+      </c>
+      <c r="F23" t="s">
+        <v>57</v>
+      </c>
+      <c r="G23" t="s">
+        <v>187</v>
+      </c>
+      <c r="H23" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" t="s">
+        <v>153</v>
+      </c>
+      <c r="D24" t="s">
+        <v>160</v>
+      </c>
+      <c r="E24" t="s">
+        <v>163</v>
+      </c>
+      <c r="F24" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H24" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" t="s">
+        <v>153</v>
+      </c>
+      <c r="D25" t="s">
+        <v>160</v>
+      </c>
+      <c r="E25" t="s">
+        <v>163</v>
+      </c>
+      <c r="F25" t="s">
+        <v>57</v>
+      </c>
+      <c r="G25" t="s">
+        <v>169</v>
+      </c>
+      <c r="H25" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -4947,81 +5258,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E2" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="H2" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="D3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="H3" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -5040,107 +5351,107 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="H2" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="D3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="H3" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="E4" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="H4" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -5150,7 +5461,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -5159,55 +5470,107 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="H2" t="s">
-        <v>184</v>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" t="s">
+        <v>192</v>
+      </c>
+      <c r="H3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
+        <v>193</v>
+      </c>
+      <c r="H4" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -5226,315 +5589,315 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E2" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="H2" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D3" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E3" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="H3" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D4" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E4" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="H4" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C5" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D5" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E5" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="H5" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E6" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="H6" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D7" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E7" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="H7" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B8" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C8" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D8" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E8" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="H8" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C9" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D9" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E9" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="H9" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="C10" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E10" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="H10" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B11" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C11" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D11" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E11" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="H11" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C12" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E12" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="H12" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
